--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/feb-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/feb-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC feb-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC feb-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">

--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/feb-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/feb-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE LOTA - SALUD</t>
+          <t>I MUNICIPALIDAD DE LOTA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -941,7 +941,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2675-29-CM26</t>
+          <t>1704-946-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -966,27 +966,27 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>53849.29</v>
+        <v>859.89</v>
       </c>
     </row>
     <row r="10">
@@ -1063,7 +1063,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1704-946-CM26</t>
+          <t>2675-29-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1088,27 +1088,27 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>859.89</v>
+        <v>53849.29</v>
       </c>
     </row>
     <row r="12">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3876-16-CM26</t>
+          <t>4099-100-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1454,17 +1454,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>69.073.300-5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>I MUNICIPALIDAD DE MARIA PINTO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2863.21</v>
+        <v>4227.59</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4099-100-CM26</t>
+          <t>3876-16-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1515,17 +1515,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.073.300-5</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIA PINTO</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>4227.59</v>
+        <v>2863.21</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1480074-3-CM26</t>
+          <t>1237404-18-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1571,32 +1571,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.255.600-3</t>
+          <t>65.293.750-0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VITACURA</t>
+          <t>CORPORACION CULTURAL MUNICIPAL DE ANCUD</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>NextTime Software S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>99.576.370-2</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>4460.72</v>
+        <v>1846.26</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1237404-18-CM26</t>
+          <t>1480074-3-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1632,17 +1632,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>65.293.750-0</t>
+          <t>69.255.600-3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>CORPORACION CULTURAL MUNICIPAL DE ANCUD</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>NextTime Software S.A.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>99.576.370-2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1846.26</v>
+        <v>4460.72</v>
       </c>
     </row>
     <row r="21">
@@ -1734,7 +1734,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3872-43-CM26</t>
+          <t>539119-470-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.040.900-3</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1523.2</v>
+        <v>1056.9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>539119-470-CM26</t>
+          <t>1238177-14-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>65.165.009-7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SEGURIDAD CIUDADANA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1056.9</v>
+        <v>3534.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1238177-14-CM26</t>
+          <t>568658-365-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1881,27 +1881,27 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>65.165.009-7</t>
+          <t>70.872.300-2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SE</t>
+          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>3534.3</v>
+        <v>30771.02</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>568658-365-CM26</t>
+          <t>4052-22-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1942,17 +1942,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>70.872.300-2</t>
+          <t>69.251.200-6</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
+          <t>I MUNICIPALIDAD DE LAGUNA BLANCA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>30771.02</v>
+        <v>10000.58</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4052-22-CM26</t>
+          <t>3872-43-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1998,32 +1998,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.251.200-6</t>
+          <t>69.040.900-3</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGUNA BLANCA</t>
+          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>10000.58</v>
+        <v>1523.2</v>
       </c>
     </row>
     <row r="27">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Departamento Administrativo de Salud Municipal.</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2348,7 +2348,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3834-43-CM26</t>
+          <t>3153-41-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2373,27 +2373,27 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>69.180.500-k</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>SUPER SOFTWARE SPA</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.486.150-7</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2403,13 +2403,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>37961</v>
+        <v>12832.96</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1238177-28-CM26</t>
+          <t>3834-43-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2434,27 +2434,27 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>65.165.009-7</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SE</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>NextTime Software S.A.</t>
+          <t>SUPER SOFTWARE SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>99.576.370-2</t>
+          <t>76.486.150-7</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>11138.4</v>
+        <v>37961</v>
       </c>
     </row>
     <row r="34">
@@ -2531,7 +2531,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3697-180-CM26</t>
+          <t>1238177-28-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2556,27 +2556,27 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.180.900-5</t>
+          <t>65.165.009-7</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICTORIA</t>
+          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SEGURIDAD CIUDADANA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>NextTime Software S.A.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>99.576.370-2</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2586,6 +2586,67 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
+        <v>11138.4</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>3697-180-CM26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>69.180.900-5</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VICTORIA</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
         <v>7096.21</v>
       </c>
     </row>

--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/feb-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/feb-2026.xlsx
@@ -562,7 +562,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +883,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +948,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1013,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1078,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1143,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1208,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1273,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1338,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1403,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1468,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1533,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1598,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1663,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1789,11 @@
           <t>92.580.000-7</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1854,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1919,11 @@
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1984,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2049,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2114,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2179,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2213,7 +2309,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2274,7 +2374,11 @@
           <t>92.580.000-7</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2335,7 +2439,11 @@
           <t>76.981.642-9</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2396,7 +2504,11 @@
           <t>92.580.000-7</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2457,7 +2569,11 @@
           <t>76.486.150-7</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2518,7 +2634,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2640,7 +2760,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/feb-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/feb-2026.xlsx
@@ -1761,7 +1761,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
